--- a/docs/downloads/08/tbl_produits_elevage_alaotra_analamiranga.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_alaotra_analamiranga.xlsx
@@ -472,9 +472,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +484,6 @@
           <t>Henan-Kisoa</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -516,9 +510,6 @@
         <is>
           <t>Vorona</t>
         </is>
-      </c>
-      <c r="C11">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
